--- a/docs/Book1.xlsx
+++ b/docs/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danny\Documents\git\Research_Methods\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BCE5B36-380B-4632-97D0-1C2DF2664ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FC30123-F142-47C6-A644-233EAC9507F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F96DA6BE-9112-44BF-BBFD-979CBF890B3D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D11F3198-4F8C-4337-91E0-DCA70E5823FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -557,7 +557,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C27478A-09E3-4460-8D80-5331AB0ABD04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6A5E3D6-C97E-476C-B886-45493544BBE5}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
